--- a/P5/qnap/data.xlsx
+++ b/P5/qnap/data.xlsx
@@ -8,63 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hexdhog/Documents/uib/CS/Y2/ACSI/P5/qnap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65C1091-FB7C-384A-910A-AFEFE4019ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CB60C1-2785-FB4B-A58D-95D695F8A290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{C3C8EABE-511B-D742-AF95-B24E6BB5453A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$96:$A$145</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$F$96:$F$145</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$J$96:$J$145</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$K$96:$K$145</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$L$96:$L$145</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$M$96:$M$145</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$Y$100</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$Y$101</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$A$96:$A$145</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$F$96:$F$145</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$J$96:$J$145</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$K$96:$K$145</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$J$96:$J$145</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$L$96:$L$145</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$M$96:$M$145</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$Y$100</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$Y$101</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$A$96:$A$145</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$F$96:$F$145</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$J$96:$J$145</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$K$96:$K$145</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Sheet1!$L$96:$L$145</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Sheet1!$M$96:$M$145</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$K$96:$K$145</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Sheet1!$Y$100</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Sheet1!$Y$101</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Sheet1!$A$96:$A$145</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Sheet1!$F$96:$F$145</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Sheet1!$J$96:$J$145</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Sheet1!$K$96:$K$145</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Sheet1!$L$96:$L$145</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Sheet1!$M$96:$M$145</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Sheet1!$Y$100</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Sheet1!$Y$101</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$L$96:$L$145</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Sheet1!$A$96:$A$145</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Sheet1!$F$96:$F$145</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Sheet1!$J$96:$J$145</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Sheet1!$K$96:$K$145</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Sheet1!$L$96:$L$145</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Sheet1!$M$96:$M$145</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Sheet1!$Y$100</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Sheet1!$Y$101</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$M$96:$M$145</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$Y$100</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$Y$101</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$A$96:$A$145</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$F$96:$F$145</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -242,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -263,7 +213,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3183,7 +3132,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>25.6</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5630,7 +5579,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>25.6</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6904,7 +6853,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>12.799999999999999</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8466,7 +8415,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>12.799999999999999</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13476,7 +13425,7 @@
       <c r="I48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="J48" s="10" t="s">
         <v>27</v>
       </c>
       <c r="K48" s="5" t="s">
@@ -13552,7 +13501,7 @@
         <v>1.4285714285714286</v>
       </c>
       <c r="K50" s="8">
-        <f t="shared" ref="J50:K78" si="4">$A5/($E$53+$E$49)</f>
+        <f t="shared" ref="K50:K78" si="4">$A5/($E$53+$E$49)</f>
         <v>0.2237136465324385</v>
       </c>
       <c r="L50" s="8">
@@ -13689,8 +13638,8 @@
         <v>9</v>
       </c>
       <c r="E54">
-        <f>ROUNDUP((E53+E49)/E52,1)</f>
-        <v>12.799999999999999</v>
+        <f>_xlfn.CEILING.MATH((E53+E49)/E52,1)</f>
+        <v>13</v>
       </c>
       <c r="G54">
         <f t="shared" si="0"/>
@@ -14539,23 +14488,23 @@
         <v>3.9149999999999997E-2</v>
       </c>
       <c r="J96">
-        <f>$Y$100</f>
+        <f t="shared" ref="J96:J127" si="7">$Y$100</f>
         <v>0.94</v>
       </c>
       <c r="K96" s="8">
-        <f>$Y$96*$A96-$Y$95</f>
+        <f t="shared" ref="K96:K127" si="8">$Y$96*$A96-$Y$95</f>
         <v>-7.76</v>
       </c>
       <c r="L96" s="8">
-        <f>$Y$97*$A96-$Y$95</f>
+        <f t="shared" ref="L96:L127" si="9">$Y$97*$A96-$Y$95</f>
         <v>-7.65</v>
       </c>
       <c r="M96" s="8">
-        <f>$Y$98*$A96-$Y$95</f>
+        <f t="shared" ref="M96:M127" si="10">$Y$98*$A96-$Y$95</f>
         <v>-7.65</v>
       </c>
       <c r="N96" s="8">
-        <f t="shared" ref="N96:N127" si="7">1/$Y$99</f>
+        <f t="shared" ref="N96:N127" si="11">1/$Y$99</f>
         <v>2.8571428571428572</v>
       </c>
       <c r="O96" s="8">
@@ -14563,7 +14512,7 @@
         <v>0.11185682326621925</v>
       </c>
       <c r="P96" s="8">
-        <f t="shared" ref="P96:R127" si="8">1/$Y$96</f>
+        <f t="shared" ref="P96:P127" si="12">1/$Y$96</f>
         <v>4.166666666666667</v>
       </c>
       <c r="Q96" s="8">
@@ -14615,23 +14564,23 @@
         <v>8.1059999999999993E-2</v>
       </c>
       <c r="J97">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K97" s="8">
-        <f>$Y$96*$A97-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-7.52</v>
       </c>
       <c r="L97" s="8">
-        <f>$Y$97*$A97-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-7.3</v>
       </c>
       <c r="M97" s="8">
-        <f>$Y$98*$A97-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-7.3</v>
       </c>
       <c r="N97" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O97" s="8">
@@ -14639,15 +14588,15 @@
         <v>0.2237136465324385</v>
       </c>
       <c r="P97" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q97" s="8">
-        <f t="shared" ref="Q96:Q127" si="9">1/$Y$97</f>
+        <f t="shared" ref="Q97:Q127" si="13">1/$Y$97</f>
         <v>2.8571428571428572</v>
       </c>
       <c r="R97" s="8">
-        <f t="shared" ref="R96:R127" si="10">1/$Y$98</f>
+        <f t="shared" ref="R97:R127" si="14">1/$Y$98</f>
         <v>2.8571428571428572</v>
       </c>
       <c r="T97" s="2" t="s">
@@ -14689,23 +14638,23 @@
         <v>0.126</v>
       </c>
       <c r="J98">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K98" s="8">
-        <f>$Y$96*$A98-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-7.28</v>
       </c>
       <c r="L98" s="8">
-        <f>$Y$97*$A98-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-6.95</v>
       </c>
       <c r="M98" s="8">
-        <f>$Y$98*$A98-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-6.95</v>
       </c>
       <c r="N98" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O98" s="8">
@@ -14713,15 +14662,15 @@
         <v>0.33557046979865773</v>
       </c>
       <c r="P98" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q98" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R98" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="T98" s="2" t="s">
@@ -14763,23 +14712,23 @@
         <v>0.17419999999999999</v>
       </c>
       <c r="J99">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K99" s="8">
-        <f>$Y$96*$A99-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-7.04</v>
       </c>
       <c r="L99" s="8">
-        <f>$Y$97*$A99-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-6.6</v>
       </c>
       <c r="M99" s="8">
-        <f>$Y$98*$A99-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-6.6</v>
       </c>
       <c r="N99" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O99" s="8">
@@ -14787,15 +14736,15 @@
         <v>0.447427293064877</v>
       </c>
       <c r="P99" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q99" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R99" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="T99" s="2" t="s">
@@ -14838,23 +14787,23 @@
         <v>0.2261</v>
       </c>
       <c r="J100">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K100" s="8">
-        <f>$Y$96*$A100-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-6.8</v>
       </c>
       <c r="L100" s="8">
-        <f>$Y$97*$A100-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-6.25</v>
       </c>
       <c r="M100" s="8">
-        <f>$Y$98*$A100-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-6.25</v>
       </c>
       <c r="N100" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O100" s="8">
@@ -14862,15 +14811,15 @@
         <v>0.5592841163310962</v>
       </c>
       <c r="P100" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q100" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R100" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="T100" s="2" t="s">
@@ -14913,23 +14862,23 @@
         <v>0.28189999999999998</v>
       </c>
       <c r="J101">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K101" s="8">
-        <f>$Y$96*$A101-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-6.5600000000000005</v>
       </c>
       <c r="L101" s="8">
-        <f>$Y$97*$A101-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-5.9</v>
       </c>
       <c r="M101" s="8">
-        <f>$Y$98*$A101-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-5.9</v>
       </c>
       <c r="N101" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O101" s="8">
@@ -14937,23 +14886,23 @@
         <v>0.67114093959731547</v>
       </c>
       <c r="P101" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q101" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R101" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="T101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="Y101">
-        <f>ROUNDUP((Y100+Y95)/Y99,1)</f>
-        <v>25.6</v>
+        <f>_xlfn.CEILING.MATH((Y100+Y95)/Y99,1)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.2">
@@ -14985,23 +14934,23 @@
         <v>0.34210000000000002</v>
       </c>
       <c r="J102">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K102" s="8">
-        <f>$Y$96*$A102-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-6.32</v>
       </c>
       <c r="L102" s="8">
-        <f>$Y$97*$A102-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-5.5500000000000007</v>
       </c>
       <c r="M102" s="8">
-        <f>$Y$98*$A102-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-5.5500000000000007</v>
       </c>
       <c r="N102" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O102" s="8">
@@ -15009,15 +14958,15 @@
         <v>0.78299776286353473</v>
       </c>
       <c r="P102" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q102" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R102" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15050,23 +14999,23 @@
         <v>0.40710000000000002</v>
       </c>
       <c r="J103">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K103" s="8">
-        <f>$Y$96*$A103-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-6.08</v>
       </c>
       <c r="L103" s="8">
-        <f>$Y$97*$A103-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-5.2</v>
       </c>
       <c r="M103" s="8">
-        <f>$Y$98*$A103-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-5.2</v>
       </c>
       <c r="N103" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O103" s="8">
@@ -15074,15 +15023,15 @@
         <v>0.89485458612975399</v>
       </c>
       <c r="P103" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q103" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R103" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15115,23 +15064,23 @@
         <v>0.4773</v>
       </c>
       <c r="J104">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K104" s="8">
-        <f>$Y$96*$A104-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-5.84</v>
       </c>
       <c r="L104" s="8">
-        <f>$Y$97*$A104-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-4.8499999999999996</v>
       </c>
       <c r="M104" s="8">
-        <f>$Y$98*$A104-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-4.8499999999999996</v>
       </c>
       <c r="N104" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O104" s="8">
@@ -15139,15 +15088,15 @@
         <v>1.0067114093959733</v>
       </c>
       <c r="P104" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q104" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R104" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15180,23 +15129,23 @@
         <v>0.5534</v>
       </c>
       <c r="J105">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K105" s="8">
-        <f>$Y$96*$A105-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-5.6</v>
       </c>
       <c r="L105" s="8">
-        <f>$Y$97*$A105-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-4.5</v>
       </c>
       <c r="M105" s="8">
-        <f>$Y$98*$A105-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-4.5</v>
       </c>
       <c r="N105" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O105" s="8">
@@ -15204,15 +15153,15 @@
         <v>1.1185682326621924</v>
       </c>
       <c r="P105" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q105" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R105" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15245,23 +15194,23 @@
         <v>0.63570000000000004</v>
       </c>
       <c r="J106">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K106" s="8">
-        <f>$Y$96*$A106-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-5.36</v>
       </c>
       <c r="L106" s="8">
-        <f>$Y$97*$A106-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-4.1500000000000004</v>
       </c>
       <c r="M106" s="8">
-        <f>$Y$98*$A106-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-4.1500000000000004</v>
       </c>
       <c r="N106" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O106" s="8">
@@ -15269,15 +15218,15 @@
         <v>1.2304250559284118</v>
       </c>
       <c r="P106" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q106" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R106" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15310,23 +15259,23 @@
         <v>0.72509999999999997</v>
       </c>
       <c r="J107">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K107" s="8">
-        <f>$Y$96*$A107-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-5.12</v>
       </c>
       <c r="L107" s="8">
-        <f>$Y$97*$A107-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-3.8000000000000007</v>
       </c>
       <c r="M107" s="8">
-        <f>$Y$98*$A107-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-3.8000000000000007</v>
       </c>
       <c r="N107" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O107" s="8">
@@ -15334,15 +15283,15 @@
         <v>1.3422818791946309</v>
       </c>
       <c r="P107" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q107" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R107" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15375,23 +15324,23 @@
         <v>0.82210000000000005</v>
       </c>
       <c r="J108">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K108" s="8">
-        <f>$Y$96*$A108-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-4.88</v>
       </c>
       <c r="L108" s="8">
-        <f>$Y$97*$A108-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-3.45</v>
       </c>
       <c r="M108" s="8">
-        <f>$Y$98*$A108-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-3.45</v>
       </c>
       <c r="N108" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O108" s="8">
@@ -15399,15 +15348,15 @@
         <v>1.4541387024608501</v>
       </c>
       <c r="P108" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q108" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R108" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15440,23 +15389,23 @@
         <v>0.92749999999999999</v>
       </c>
       <c r="J109">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K109" s="8">
-        <f>$Y$96*$A109-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-4.6400000000000006</v>
       </c>
       <c r="L109" s="8">
-        <f>$Y$97*$A109-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-3.1000000000000005</v>
       </c>
       <c r="M109" s="8">
-        <f>$Y$98*$A109-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-3.1000000000000005</v>
       </c>
       <c r="N109" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O109" s="8">
@@ -15464,15 +15413,15 @@
         <v>1.5659955257270695</v>
       </c>
       <c r="P109" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q109" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R109" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15505,23 +15454,23 @@
         <v>1.042</v>
       </c>
       <c r="J110">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K110" s="8">
-        <f>$Y$96*$A110-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-4.4000000000000004</v>
       </c>
       <c r="L110" s="8">
-        <f>$Y$97*$A110-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-2.75</v>
       </c>
       <c r="M110" s="8">
-        <f>$Y$98*$A110-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-2.75</v>
       </c>
       <c r="N110" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O110" s="8">
@@ -15529,15 +15478,15 @@
         <v>1.6778523489932886</v>
       </c>
       <c r="P110" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q110" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R110" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15570,23 +15519,23 @@
         <v>1.1659999999999999</v>
       </c>
       <c r="J111">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K111" s="8">
-        <f>$Y$96*$A111-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-4.16</v>
       </c>
       <c r="L111" s="8">
-        <f>$Y$97*$A111-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-2.4000000000000004</v>
       </c>
       <c r="M111" s="8">
-        <f>$Y$98*$A111-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-2.4000000000000004</v>
       </c>
       <c r="N111" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O111" s="8">
@@ -15594,15 +15543,15 @@
         <v>1.789709172259508</v>
       </c>
       <c r="P111" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q111" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R111" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15635,23 +15584,23 @@
         <v>1.302</v>
       </c>
       <c r="J112">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K112" s="8">
-        <f>$Y$96*$A112-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-3.92</v>
       </c>
       <c r="L112" s="8">
-        <f>$Y$97*$A112-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-2.0500000000000007</v>
       </c>
       <c r="M112" s="8">
-        <f>$Y$98*$A112-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-2.0500000000000007</v>
       </c>
       <c r="N112" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O112" s="8">
@@ -15659,15 +15608,15 @@
         <v>1.9015659955257271</v>
       </c>
       <c r="P112" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q112" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R112" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15700,23 +15649,23 @@
         <v>1.4490000000000001</v>
       </c>
       <c r="J113">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K113" s="8">
-        <f>$Y$96*$A113-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-3.6799999999999997</v>
       </c>
       <c r="L113" s="8">
-        <f>$Y$97*$A113-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-1.7000000000000002</v>
       </c>
       <c r="M113" s="8">
-        <f>$Y$98*$A113-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-1.7000000000000002</v>
       </c>
       <c r="N113" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O113" s="8">
@@ -15724,15 +15673,15 @@
         <v>2.0134228187919465</v>
       </c>
       <c r="P113" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q113" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R113" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15765,23 +15714,23 @@
         <v>1.6080000000000001</v>
       </c>
       <c r="J114">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K114" s="8">
-        <f>$Y$96*$A114-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-3.4400000000000004</v>
       </c>
       <c r="L114" s="8">
-        <f>$Y$97*$A114-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-1.3500000000000005</v>
       </c>
       <c r="M114" s="8">
-        <f>$Y$98*$A114-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-1.3500000000000005</v>
       </c>
       <c r="N114" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O114" s="8">
@@ -15789,15 +15738,15 @@
         <v>2.1252796420581657</v>
       </c>
       <c r="P114" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q114" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R114" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15830,23 +15779,23 @@
         <v>1.7809999999999999</v>
       </c>
       <c r="J115">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K115" s="8">
-        <f>$Y$96*$A115-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-3.2</v>
       </c>
       <c r="L115" s="8">
-        <f>$Y$97*$A115-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="M115" s="8">
-        <f>$Y$98*$A115-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
       <c r="N115" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O115" s="8">
@@ -15854,15 +15803,15 @@
         <v>2.2371364653243848</v>
       </c>
       <c r="P115" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q115" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R115" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15895,23 +15844,23 @@
         <v>1.968</v>
       </c>
       <c r="J116">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K116" s="8">
-        <f>$Y$96*$A116-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-2.96</v>
       </c>
       <c r="L116" s="8">
-        <f>$Y$97*$A116-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-0.65000000000000036</v>
       </c>
       <c r="M116" s="8">
-        <f>$Y$98*$A116-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-0.65000000000000036</v>
       </c>
       <c r="N116" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O116" s="8">
@@ -15919,15 +15868,15 @@
         <v>2.348993288590604</v>
       </c>
       <c r="P116" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q116" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R116" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -15960,23 +15909,23 @@
         <v>2.17</v>
       </c>
       <c r="J117">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K117" s="8">
-        <f>$Y$96*$A117-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-2.7200000000000006</v>
       </c>
       <c r="L117" s="8">
-        <f>$Y$97*$A117-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>-0.30000000000000071</v>
       </c>
       <c r="M117" s="8">
-        <f>$Y$98*$A117-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>-0.30000000000000071</v>
       </c>
       <c r="N117" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O117" s="8">
@@ -15984,15 +15933,15 @@
         <v>2.4608501118568236</v>
       </c>
       <c r="P117" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q117" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R117" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16025,23 +15974,23 @@
         <v>2.3879999999999999</v>
       </c>
       <c r="J118">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K118" s="8">
-        <f>$Y$96*$A118-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-2.4800000000000004</v>
       </c>
       <c r="L118" s="8">
-        <f>$Y$97*$A118-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>4.9999999999998934E-2</v>
       </c>
       <c r="M118" s="8">
-        <f>$Y$98*$A118-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>4.9999999999998934E-2</v>
       </c>
       <c r="N118" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O118" s="8">
@@ -16049,15 +15998,15 @@
         <v>2.5727069351230427</v>
       </c>
       <c r="P118" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q118" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R118" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16090,23 +16039,23 @@
         <v>2.6219999999999999</v>
       </c>
       <c r="J119">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K119" s="8">
-        <f>$Y$96*$A119-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-2.2400000000000002</v>
       </c>
       <c r="L119" s="8">
-        <f>$Y$97*$A119-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>0.39999999999999858</v>
       </c>
       <c r="M119" s="8">
-        <f>$Y$98*$A119-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>0.39999999999999858</v>
       </c>
       <c r="N119" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O119" s="8">
@@ -16114,15 +16063,15 @@
         <v>2.6845637583892619</v>
       </c>
       <c r="P119" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q119" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R119" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16155,23 +16104,23 @@
         <v>2.8730000000000002</v>
       </c>
       <c r="J120">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K120" s="8">
-        <f>$Y$96*$A120-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-2</v>
       </c>
       <c r="L120" s="8">
-        <f>$Y$97*$A120-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>0.75</v>
       </c>
       <c r="M120" s="8">
-        <f>$Y$98*$A120-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>0.75</v>
       </c>
       <c r="N120" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O120" s="8">
@@ -16179,15 +16128,15 @@
         <v>2.796420581655481</v>
       </c>
       <c r="P120" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q120" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R120" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16220,23 +16169,23 @@
         <v>3.141</v>
       </c>
       <c r="J121">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K121" s="8">
-        <f>$Y$96*$A121-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-1.7599999999999998</v>
       </c>
       <c r="L121" s="8">
-        <f>$Y$97*$A121-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>1.0999999999999996</v>
       </c>
       <c r="M121" s="8">
-        <f>$Y$98*$A121-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>1.0999999999999996</v>
       </c>
       <c r="N121" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O121" s="8">
@@ -16244,15 +16193,15 @@
         <v>2.9082774049217002</v>
       </c>
       <c r="P121" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q121" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R121" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16285,23 +16234,23 @@
         <v>3.4260000000000002</v>
       </c>
       <c r="J122">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K122" s="8">
-        <f>$Y$96*$A122-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-1.5200000000000005</v>
       </c>
       <c r="L122" s="8">
-        <f>$Y$97*$A122-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>1.4499999999999993</v>
       </c>
       <c r="M122" s="8">
-        <f>$Y$98*$A122-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>1.4499999999999993</v>
       </c>
       <c r="N122" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O122" s="8">
@@ -16309,15 +16258,15 @@
         <v>3.0201342281879198</v>
       </c>
       <c r="P122" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q122" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R122" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16350,23 +16299,23 @@
         <v>3.7280000000000002</v>
       </c>
       <c r="J123">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K123" s="8">
-        <f>$Y$96*$A123-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-1.2800000000000002</v>
       </c>
       <c r="L123" s="8">
-        <f>$Y$97*$A123-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>1.7999999999999989</v>
       </c>
       <c r="M123" s="8">
-        <f>$Y$98*$A123-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>1.7999999999999989</v>
       </c>
       <c r="N123" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O123" s="8">
@@ -16374,15 +16323,15 @@
         <v>3.1319910514541389</v>
       </c>
       <c r="P123" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q123" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R123" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16415,23 +16364,23 @@
         <v>4.0460000000000003</v>
       </c>
       <c r="J124">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K124" s="8">
-        <f>$Y$96*$A124-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-1.04</v>
       </c>
       <c r="L124" s="8">
-        <f>$Y$97*$A124-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>2.1499999999999986</v>
       </c>
       <c r="M124" s="8">
-        <f>$Y$98*$A124-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>2.1499999999999986</v>
       </c>
       <c r="N124" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O124" s="8">
@@ -16439,15 +16388,15 @@
         <v>3.2438478747203581</v>
       </c>
       <c r="P124" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q124" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R124" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16480,23 +16429,23 @@
         <v>4.3810000000000002</v>
       </c>
       <c r="J125">
-        <f>$Y$100</f>
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K125" s="8">
-        <f>$Y$96*$A125-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-0.80000000000000071</v>
       </c>
       <c r="L125" s="8">
-        <f>$Y$97*$A125-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
       <c r="M125" s="8">
-        <f>$Y$98*$A125-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
       <c r="N125" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O125" s="8">
@@ -16504,15 +16453,15 @@
         <v>3.3557046979865772</v>
       </c>
       <c r="P125" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q125" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R125" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16544,24 +16493,24 @@
       <c r="I126">
         <v>4.7300000000000004</v>
       </c>
-      <c r="J126" s="10">
-        <f>$Y$100</f>
+      <c r="J126">
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K126" s="8">
-        <f>$Y$96*$A126-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-0.5600000000000005</v>
       </c>
       <c r="L126" s="8">
-        <f>$Y$97*$A126-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>2.8499999999999996</v>
       </c>
       <c r="M126" s="8">
-        <f>$Y$98*$A126-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>2.8499999999999996</v>
       </c>
       <c r="N126" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O126" s="8">
@@ -16569,15 +16518,15 @@
         <v>3.4675615212527968</v>
       </c>
       <c r="P126" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q126" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R126" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16609,24 +16558,24 @@
       <c r="I127">
         <v>5.0949999999999998</v>
       </c>
-      <c r="J127" s="10">
-        <f>$Y$100</f>
+      <c r="J127">
+        <f t="shared" si="7"/>
         <v>0.94</v>
       </c>
       <c r="K127" s="8">
-        <f>$Y$96*$A127-$Y$95</f>
+        <f t="shared" si="8"/>
         <v>-0.32000000000000028</v>
       </c>
       <c r="L127" s="8">
-        <f>$Y$97*$A127-$Y$95</f>
+        <f t="shared" si="9"/>
         <v>3.1999999999999993</v>
       </c>
       <c r="M127" s="8">
-        <f>$Y$98*$A127-$Y$95</f>
+        <f t="shared" si="10"/>
         <v>3.1999999999999993</v>
       </c>
       <c r="N127" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O127" s="8">
@@ -16634,15 +16583,15 @@
         <v>3.579418344519016</v>
       </c>
       <c r="P127" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q127" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R127" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16674,24 +16623,24 @@
       <c r="I128">
         <v>5.4720000000000004</v>
       </c>
-      <c r="J128" s="10">
-        <f>$Y$100</f>
+      <c r="J128">
+        <f t="shared" ref="J128:J145" si="15">$Y$100</f>
         <v>0.94</v>
       </c>
       <c r="K128" s="8">
-        <f>$Y$96*$A128-$Y$95</f>
+        <f t="shared" ref="K128:K145" si="16">$Y$96*$A128-$Y$95</f>
         <v>-8.0000000000000071E-2</v>
       </c>
       <c r="L128" s="8">
-        <f>$Y$97*$A128-$Y$95</f>
+        <f t="shared" ref="L128:L145" si="17">$Y$97*$A128-$Y$95</f>
         <v>3.5499999999999989</v>
       </c>
       <c r="M128" s="8">
-        <f>$Y$98*$A128-$Y$95</f>
+        <f t="shared" ref="M128:M145" si="18">$Y$98*$A128-$Y$95</f>
         <v>3.5499999999999989</v>
       </c>
       <c r="N128" s="8">
-        <f t="shared" ref="N128:N145" si="11">1/$Y$99</f>
+        <f t="shared" ref="N128:N145" si="19">1/$Y$99</f>
         <v>2.8571428571428572</v>
       </c>
       <c r="O128" s="8">
@@ -16699,15 +16648,15 @@
         <v>3.6912751677852351</v>
       </c>
       <c r="P128" s="8">
-        <f t="shared" ref="P128:P145" si="12">1/$Y$96</f>
+        <f t="shared" ref="P128:P145" si="20">1/$Y$96</f>
         <v>4.166666666666667</v>
       </c>
       <c r="Q128" s="8">
-        <f t="shared" ref="Q128:Q145" si="13">1/$Y$97</f>
+        <f t="shared" ref="Q128:Q145" si="21">1/$Y$97</f>
         <v>2.8571428571428572</v>
       </c>
       <c r="R128" s="8">
-        <f t="shared" ref="R128:R145" si="14">1/$Y$98</f>
+        <f t="shared" ref="R128:R145" si="22">1/$Y$98</f>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16739,24 +16688,24 @@
       <c r="I129">
         <v>5.8620000000000001</v>
       </c>
-      <c r="J129" s="10">
-        <f>$Y$100</f>
+      <c r="J129">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K129" s="8">
-        <f>$Y$96*$A129-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>0.16000000000000014</v>
       </c>
       <c r="L129" s="8">
-        <f>$Y$97*$A129-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>3.8999999999999986</v>
       </c>
       <c r="M129" s="8">
-        <f>$Y$98*$A129-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>3.8999999999999986</v>
       </c>
       <c r="N129" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O129" s="8">
@@ -16764,15 +16713,15 @@
         <v>3.8031319910514543</v>
       </c>
       <c r="P129" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q129" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R129" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16804,24 +16753,24 @@
       <c r="I130">
         <v>6.2629999999999999</v>
       </c>
-      <c r="J130" s="10">
-        <f>$Y$100</f>
+      <c r="J130">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K130" s="8">
-        <f>$Y$96*$A130-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>0.40000000000000036</v>
       </c>
       <c r="L130" s="8">
-        <f>$Y$97*$A130-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>4.25</v>
       </c>
       <c r="M130" s="8">
-        <f>$Y$98*$A130-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>4.25</v>
       </c>
       <c r="N130" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O130" s="8">
@@ -16829,15 +16778,15 @@
         <v>3.9149888143176734</v>
       </c>
       <c r="P130" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q130" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R130" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16869,24 +16818,24 @@
       <c r="I131">
         <v>6.6749999999999998</v>
       </c>
-      <c r="J131" s="10">
-        <f>$Y$100</f>
+      <c r="J131">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K131" s="8">
-        <f>$Y$96*$A131-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>0.64000000000000057</v>
       </c>
       <c r="L131" s="8">
-        <f>$Y$97*$A131-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="M131" s="8">
-        <f>$Y$98*$A131-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="N131" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O131" s="8">
@@ -16894,15 +16843,15 @@
         <v>4.026845637583893</v>
       </c>
       <c r="P131" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q131" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R131" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16934,24 +16883,24 @@
       <c r="I132">
         <v>7.0960000000000001</v>
       </c>
-      <c r="J132" s="10">
-        <f>$Y$100</f>
+      <c r="J132">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K132" s="8">
-        <f>$Y$96*$A132-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>0.87999999999999901</v>
       </c>
       <c r="L132" s="8">
-        <f>$Y$97*$A132-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>4.9499999999999993</v>
       </c>
       <c r="M132" s="8">
-        <f>$Y$98*$A132-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>4.9499999999999993</v>
       </c>
       <c r="N132" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O132" s="8">
@@ -16959,15 +16908,15 @@
         <v>4.1387024608501122</v>
       </c>
       <c r="P132" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q132" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R132" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -16999,24 +16948,24 @@
       <c r="I133">
         <v>7.5250000000000004</v>
       </c>
-      <c r="J133" s="10">
-        <f>$Y$100</f>
+      <c r="J133">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K133" s="8">
-        <f>$Y$96*$A133-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>1.1199999999999992</v>
       </c>
       <c r="L133" s="8">
-        <f>$Y$97*$A133-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>5.2999999999999989</v>
       </c>
       <c r="M133" s="8">
-        <f>$Y$98*$A133-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>5.2999999999999989</v>
       </c>
       <c r="N133" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O133" s="8">
@@ -17024,15 +16973,15 @@
         <v>4.2505592841163313</v>
       </c>
       <c r="P133" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q133" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R133" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17064,24 +17013,24 @@
       <c r="I134">
         <v>7.9610000000000003</v>
       </c>
-      <c r="J134" s="10">
-        <f>$Y$100</f>
+      <c r="J134">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K134" s="8">
-        <f>$Y$96*$A134-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>1.3599999999999994</v>
       </c>
       <c r="L134" s="8">
-        <f>$Y$97*$A134-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>5.6499999999999986</v>
       </c>
       <c r="M134" s="8">
-        <f>$Y$98*$A134-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>5.6499999999999986</v>
       </c>
       <c r="N134" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O134" s="8">
@@ -17089,15 +17038,15 @@
         <v>4.3624161073825505</v>
       </c>
       <c r="P134" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q134" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R134" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17129,24 +17078,24 @@
       <c r="I135">
         <v>8.4030000000000005</v>
       </c>
-      <c r="J135" s="10">
-        <f>$Y$100</f>
+      <c r="J135">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K135" s="8">
-        <f>$Y$96*$A135-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>1.5999999999999996</v>
       </c>
       <c r="L135" s="8">
-        <f>$Y$97*$A135-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="M135" s="8">
-        <f>$Y$98*$A135-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>6</v>
       </c>
       <c r="N135" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O135" s="8">
@@ -17154,15 +17103,15 @@
         <v>4.4742729306487696</v>
       </c>
       <c r="P135" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q135" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R135" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17194,24 +17143,24 @@
       <c r="I136">
         <v>8.8520000000000003</v>
       </c>
-      <c r="J136" s="10">
-        <f>$Y$100</f>
+      <c r="J136">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K136" s="8">
-        <f>$Y$96*$A136-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>1.8399999999999999</v>
       </c>
       <c r="L136" s="8">
-        <f>$Y$97*$A136-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>6.35</v>
       </c>
       <c r="M136" s="8">
-        <f>$Y$98*$A136-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>6.35</v>
       </c>
       <c r="N136" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O136" s="8">
@@ -17219,15 +17168,15 @@
         <v>4.5861297539149888</v>
       </c>
       <c r="P136" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q136" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R136" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17259,24 +17208,24 @@
       <c r="I137">
         <v>9.3049999999999997</v>
       </c>
-      <c r="J137" s="10">
-        <f>$Y$100</f>
+      <c r="J137">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K137" s="8">
-        <f>$Y$96*$A137-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>2.08</v>
       </c>
       <c r="L137" s="8">
-        <f>$Y$97*$A137-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>6.6999999999999993</v>
       </c>
       <c r="M137" s="8">
-        <f>$Y$98*$A137-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>6.6999999999999993</v>
       </c>
       <c r="N137" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O137" s="8">
@@ -17284,15 +17233,15 @@
         <v>4.6979865771812079</v>
       </c>
       <c r="P137" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q137" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R137" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17324,24 +17273,24 @@
       <c r="I138">
         <v>9.7629999999999999</v>
       </c>
-      <c r="J138" s="10">
-        <f>$Y$100</f>
+      <c r="J138">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K138" s="8">
-        <f>$Y$96*$A138-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>2.3200000000000003</v>
       </c>
       <c r="L138" s="8">
-        <f>$Y$97*$A138-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>7.0499999999999989</v>
       </c>
       <c r="M138" s="8">
-        <f>$Y$98*$A138-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>7.0499999999999989</v>
       </c>
       <c r="N138" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O138" s="8">
@@ -17349,15 +17298,15 @@
         <v>4.809843400447428</v>
       </c>
       <c r="P138" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q138" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R138" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17389,24 +17338,24 @@
       <c r="I139">
         <v>10.220000000000001</v>
       </c>
-      <c r="J139" s="10">
-        <f>$Y$100</f>
+      <c r="J139">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K139" s="8">
-        <f>$Y$96*$A139-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>2.5599999999999987</v>
       </c>
       <c r="L139" s="8">
-        <f>$Y$97*$A139-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>7.3999999999999986</v>
       </c>
       <c r="M139" s="8">
-        <f>$Y$98*$A139-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>7.3999999999999986</v>
       </c>
       <c r="N139" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O139" s="8">
@@ -17414,15 +17363,15 @@
         <v>4.9217002237136471</v>
       </c>
       <c r="P139" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q139" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R139" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17454,24 +17403,24 @@
       <c r="I140">
         <v>10.69</v>
       </c>
-      <c r="J140" s="10">
-        <f>$Y$100</f>
+      <c r="J140">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K140" s="8">
-        <f>$Y$96*$A140-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>2.7999999999999989</v>
       </c>
       <c r="L140" s="8">
-        <f>$Y$97*$A140-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>7.7499999999999982</v>
       </c>
       <c r="M140" s="8">
-        <f>$Y$98*$A140-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>7.7499999999999982</v>
       </c>
       <c r="N140" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O140" s="8">
@@ -17479,15 +17428,15 @@
         <v>5.0335570469798663</v>
       </c>
       <c r="P140" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q140" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R140" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17519,24 +17468,24 @@
       <c r="I141">
         <v>11.16</v>
       </c>
-      <c r="J141" s="10">
-        <f>$Y$100</f>
+      <c r="J141">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K141" s="8">
-        <f>$Y$96*$A141-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>3.0399999999999991</v>
       </c>
       <c r="L141" s="8">
-        <f>$Y$97*$A141-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>8.0999999999999979</v>
       </c>
       <c r="M141" s="8">
-        <f>$Y$98*$A141-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>8.0999999999999979</v>
       </c>
       <c r="N141" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O141" s="8">
@@ -17544,15 +17493,15 @@
         <v>5.1454138702460854</v>
       </c>
       <c r="P141" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q141" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R141" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17584,24 +17533,24 @@
       <c r="I142">
         <v>11.63</v>
       </c>
-      <c r="J142" s="10">
-        <f>$Y$100</f>
+      <c r="J142">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K142" s="8">
-        <f>$Y$96*$A142-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>3.2799999999999994</v>
       </c>
       <c r="L142" s="8">
-        <f>$Y$97*$A142-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>8.4499999999999993</v>
       </c>
       <c r="M142" s="8">
-        <f>$Y$98*$A142-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>8.4499999999999993</v>
       </c>
       <c r="N142" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O142" s="8">
@@ -17609,15 +17558,15 @@
         <v>5.2572706935123046</v>
       </c>
       <c r="P142" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q142" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R142" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17649,24 +17598,24 @@
       <c r="I143">
         <v>12.1</v>
       </c>
-      <c r="J143" s="10">
-        <f>$Y$100</f>
+      <c r="J143">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K143" s="8">
-        <f>$Y$96*$A143-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>3.5199999999999996</v>
       </c>
       <c r="L143" s="8">
-        <f>$Y$97*$A143-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>8.7999999999999972</v>
       </c>
       <c r="M143" s="8">
-        <f>$Y$98*$A143-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>8.7999999999999972</v>
       </c>
       <c r="N143" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O143" s="8">
@@ -17674,15 +17623,15 @@
         <v>5.3691275167785237</v>
       </c>
       <c r="P143" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q143" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R143" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17714,24 +17663,24 @@
       <c r="I144">
         <v>12.58</v>
       </c>
-      <c r="J144" s="10">
-        <f>$Y$100</f>
+      <c r="J144">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K144" s="8">
-        <f>$Y$96*$A144-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>3.76</v>
       </c>
       <c r="L144" s="8">
-        <f>$Y$97*$A144-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>9.1499999999999986</v>
       </c>
       <c r="M144" s="8">
-        <f>$Y$98*$A144-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>9.1499999999999986</v>
       </c>
       <c r="N144" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O144" s="8">
@@ -17739,15 +17688,15 @@
         <v>5.4809843400447429</v>
       </c>
       <c r="P144" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q144" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R144" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>
@@ -17779,24 +17728,24 @@
       <c r="I145">
         <v>13.05</v>
       </c>
-      <c r="J145" s="10">
-        <f>$Y$100</f>
+      <c r="J145">
+        <f t="shared" si="15"/>
         <v>0.94</v>
       </c>
       <c r="K145" s="8">
-        <f>$Y$96*$A145-$Y$95</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="L145" s="8">
-        <f>$Y$97*$A145-$Y$95</f>
+        <f t="shared" si="17"/>
         <v>9.5</v>
       </c>
       <c r="M145" s="8">
-        <f>$Y$98*$A145-$Y$95</f>
+        <f t="shared" si="18"/>
         <v>9.5</v>
       </c>
       <c r="N145" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="O145" s="8">
@@ -17804,15 +17753,15 @@
         <v>5.592841163310962</v>
       </c>
       <c r="P145" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>4.166666666666667</v>
       </c>
       <c r="Q145" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>2.8571428571428572</v>
       </c>
       <c r="R145" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>2.8571428571428572</v>
       </c>
     </row>

--- a/P5/qnap/data.xlsx
+++ b/P5/qnap/data.xlsx
@@ -8,13 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hexdhog/Documents/uib/CS/Y2/ACSI/P5/qnap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CB60C1-2785-FB4B-A58D-95D695F8A290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F609419E-6311-0744-BA17-9308BEBAB8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{C3C8EABE-511B-D742-AF95-B24E6BB5453A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$4:$A$33</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$E$4:$E$33</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$E$54</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$G$49:$G$78</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$H$49:$H$78</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$I$49:$I$78</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$E$53</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$E$54</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$G$49:$G$78</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$H$49:$H$78</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$I$49:$I$78</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$A$4:$A$33</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$E$4:$E$33</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$E$53</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -6846,6 +6862,43 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:errBars>
+            <c:errDir val="x"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="1"/>
+            <c:val val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="0"/>
+            <c:val val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$E$54</c:f>
